--- a/data/trans_camb/P15-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P15-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 6,64</t>
+          <t>-1,54; 7,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 3,91</t>
+          <t>-4,53; 3,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,1; -0,73</t>
+          <t>-9,98; -0,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 5,85</t>
+          <t>-0,59; 5,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,77</t>
+          <t>-2,82; 2,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 6,65</t>
+          <t>-2,14; 6,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 5,24</t>
+          <t>-0,1; 5,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,47</t>
+          <t>-2,73; 2,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 1,31</t>
+          <t>-5,33; 1,11</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 75,96</t>
+          <t>-12,6; 79,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,18; 43,8</t>
+          <t>-35,8; 46,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-81,31; -3,35</t>
+          <t>-81,86; -3,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 158,33</t>
+          <t>-11,1; 156,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,24; 79,39</t>
+          <t>-48,23; 80,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,59; 200,14</t>
+          <t>-42,64; 185,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 81,04</t>
+          <t>-3,38; 72,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,25; 39,57</t>
+          <t>-30,8; 33,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-62,67; 19,29</t>
+          <t>-60,46; 19,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 6,26</t>
+          <t>-0,07; 6,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 2,82</t>
+          <t>-3,36; 2,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 1,9</t>
+          <t>-5,77; 1,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 4,14</t>
+          <t>-2,33; 3,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,86</t>
+          <t>-4,17; 0,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,7; -0,01</t>
+          <t>-5,49; -0,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 4,25</t>
+          <t>-0,09; 4,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 0,96</t>
+          <t>-2,87; 1,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,83; -0,17</t>
+          <t>-5,11; -0,49</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 84,48</t>
+          <t>-0,82; 94,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 37,69</t>
+          <t>-32,86; 42,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,78; 24,45</t>
+          <t>-58,56; 27,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,2; 99,04</t>
+          <t>-32,51; 74,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,28; 21,76</t>
+          <t>-57,24; 22,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-75,73; 1,84</t>
+          <t>-76,56; 1,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 68,95</t>
+          <t>-1,05; 63,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,09; 14,94</t>
+          <t>-34,77; 18,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-59,5; -2,48</t>
+          <t>-62,95; -6,47</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 4,22</t>
+          <t>-1,89; 4,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 1,0</t>
+          <t>-4,73; 1,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 2,63</t>
+          <t>-3,39; 2,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,22</t>
+          <t>-0,78; 3,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,87</t>
+          <t>-1,03; 3,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,2</t>
+          <t>0,25; 4,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,88</t>
+          <t>-0,52; 3,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,2</t>
+          <t>-1,97; 1,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,74</t>
+          <t>-0,78; 2,93</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 73,75</t>
+          <t>-23,14; 76,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,5; 18,14</t>
+          <t>-52,35; 19,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-39,02; 45,36</t>
+          <t>-38,78; 52,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,65; 174,41</t>
+          <t>-21,96; 152,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,75; 133,69</t>
+          <t>-31,52; 160,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 202,15</t>
+          <t>4,97; 208,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 71,42</t>
+          <t>-10,58; 82,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,79; 27,78</t>
+          <t>-35,77; 30,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 64,11</t>
+          <t>-13,31; 70,99</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 1,33</t>
+          <t>-5,03; 1,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,59; -0,73</t>
+          <t>-6,49; -0,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 1,17</t>
+          <t>-6,91; 1,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 4,41</t>
+          <t>-0,72; 4,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,32</t>
+          <t>-2,31; 2,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,11</t>
+          <t>-2,02; 2,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 2,0</t>
+          <t>-2,07; 2,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,18</t>
+          <t>-3,75; 0,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 1,06</t>
+          <t>-3,68; 1,09</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,9; 24,23</t>
+          <t>-51,58; 21,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-65,76; -9,44</t>
+          <t>-66,38; -5,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-72,69; 15,86</t>
+          <t>-70,71; 26,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 152,87</t>
+          <t>-14,97; 176,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,03; 91,15</t>
+          <t>-46,05; 99,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,93; 79,99</t>
+          <t>-38,49; 85,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,3; 41,57</t>
+          <t>-29,47; 42,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-51,12; 4,27</t>
+          <t>-52,79; 1,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,17; 18,89</t>
+          <t>-53,44; 21,56</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 0,54</t>
+          <t>-4,76; 0,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 0,45</t>
+          <t>-4,54; 0,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 3,01</t>
+          <t>-2,71; 3,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 8,52</t>
+          <t>1,31; 8,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 4,82</t>
+          <t>-1,3; 4,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,53</t>
+          <t>-1,12; 4,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,95</t>
+          <t>-0,74; 3,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,94</t>
+          <t>-2,06; 1,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,96</t>
+          <t>-0,83; 3,06</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-71,93; 18,76</t>
+          <t>-72,96; 20,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-72,29; 19,28</t>
+          <t>-69,24; 25,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-38,29; 95,78</t>
+          <t>-41,26; 94,46</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17,62; 293,67</t>
+          <t>20,86; 265,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-27,0; 152,15</t>
+          <t>-26,59; 153,02</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 156,68</t>
+          <t>-19,11; 146,93</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 107,56</t>
+          <t>-13,54; 101,13</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-38,23; 51,65</t>
+          <t>-37,49; 52,62</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 82,55</t>
+          <t>-14,0; 86,77</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 5,23</t>
+          <t>-1,25; 5,51</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 2,4</t>
+          <t>-3,68; 2,31</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,26</t>
+          <t>-2,29; 3,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 3,76</t>
+          <t>-3,9; 3,4</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 4,16</t>
+          <t>-3,73; 4,04</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 2,02</t>
+          <t>-7,52; 1,91</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,56</t>
+          <t>-1,78; 3,46</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 2,49</t>
+          <t>-2,56; 2,64</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 1,7</t>
+          <t>-4,21; 1,5</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 228,8</t>
+          <t>-27,78; 221,94</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-65,16; 110,81</t>
+          <t>-68,4; 93,99</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-42,11; 142,86</t>
+          <t>-43,21; 152,24</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-46,37; 71,0</t>
+          <t>-41,1; 62,45</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-38,86; 78,04</t>
+          <t>-38,64; 71,98</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-73,41; 30,86</t>
+          <t>-73,71; 29,11</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-27,48; 80,72</t>
+          <t>-27,51; 80,18</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-36,1; 58,87</t>
+          <t>-36,57; 58,69</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-54,19; 34,13</t>
+          <t>-58,64; 32,27</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,5; 9,62</t>
+          <t>0,18; 8,96</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 5,27</t>
+          <t>-1,95; 5,35</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 6,59</t>
+          <t>-0,42; 6,6</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 8,9</t>
+          <t>-1,52; 8,74</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 4,69</t>
+          <t>-5,09; 4,84</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 6,28</t>
+          <t>-2,22; 6,1</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,69; 7,47</t>
+          <t>0,21; 7,52</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 3,9</t>
+          <t>-2,85; 4,09</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 5,19</t>
+          <t>-0,37; 5,18</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 382,32</t>
+          <t>-0,47; 390,13</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 245,4</t>
+          <t>-35,19; 240,75</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 317,49</t>
+          <t>-12,12; 293,18</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 112,32</t>
+          <t>-14,32; 115,11</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 61,25</t>
+          <t>-38,83; 62,53</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 85,86</t>
+          <t>-16,57; 86,23</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,14; 120,88</t>
+          <t>-0,18; 117,88</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-28,58; 63,7</t>
+          <t>-29,87; 68,95</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 84,72</t>
+          <t>-4,73; 82,11</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,41</t>
+          <t>-0,28; 2,22</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -0,32</t>
+          <t>-2,71; -0,29</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,27; -0,23</t>
+          <t>-3,3; -0,26</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,24</t>
+          <t>0,88; 3,18</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,36</t>
+          <t>-0,94; 1,28</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,92</t>
+          <t>-0,62; 1,71</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,4</t>
+          <t>0,65; 2,44</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,24</t>
+          <t>-1,39; 0,19</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,45</t>
+          <t>-1,6; 0,45</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 36,24</t>
+          <t>-3,48; 32,82</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-34,96; -5,06</t>
+          <t>-33,32; -3,96</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-41,03; -3,14</t>
+          <t>-41,11; -3,8</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12,14; 67,82</t>
+          <t>15,42; 67,5</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 29,61</t>
+          <t>-15,8; 27,4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 40,77</t>
+          <t>-10,95; 36,65</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,49; 41,1</t>
+          <t>9,39; 41,84</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 4,09</t>
+          <t>-21,22; 3,2</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 7,79</t>
+          <t>-24,27; 7,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P15-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P15-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-5,96</t>
+          <t>-5,67</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,38</t>
+          <t>-2,24</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 7,0</t>
+          <t>-1,86; 6,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 3,95</t>
+          <t>-4,29; 3,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,98; -0,72</t>
+          <t>-9,61; -0,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 5,67</t>
+          <t>-0,64; 5,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 2,75</t>
+          <t>-3,22; 2,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 6,39</t>
+          <t>-2,23; 6,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 5,03</t>
+          <t>0,04; 5,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 2,21</t>
+          <t>-2,86; 2,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 1,11</t>
+          <t>-5,06; 1,08</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-55,47%</t>
+          <t>-52,76%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-30,29%</t>
+          <t>-28,48%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 79,54</t>
+          <t>-15,32; 72,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,8; 46,19</t>
+          <t>-35,95; 48,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-81,86; -3,75</t>
+          <t>-80,36; -3,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 156,61</t>
+          <t>-13,14; 158,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,23; 80,77</t>
+          <t>-51,43; 67,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,64; 185,38</t>
+          <t>-40,87; 178,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 72,59</t>
+          <t>0,11; 79,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 33,03</t>
+          <t>-31,84; 31,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-60,46; 19,21</t>
+          <t>-59,19; 17,08</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-1,81</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,71</t>
+          <t>-2,58</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,81</t>
+          <t>-2,37</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 6,73</t>
+          <t>0,16; 6,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,91</t>
+          <t>-3,23; 2,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 1,8</t>
+          <t>-5,41; 2,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 3,35</t>
+          <t>-2,21; 3,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,76</t>
+          <t>-4,11; 1,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,49; -0,13</t>
+          <t>-5,1; -0,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 4,16</t>
+          <t>-0,24; 4,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 1,17</t>
+          <t>-3,12; 1,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,11; -0,49</t>
+          <t>-4,49; 0,14</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-26,61%</t>
+          <t>-20,64%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-48,08%</t>
+          <t>-45,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-38,39%</t>
+          <t>-32,31%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 94,24</t>
+          <t>-0,56; 89,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,86; 42,07</t>
+          <t>-31,07; 38,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,56; 27,31</t>
+          <t>-54,12; 34,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,51; 74,84</t>
+          <t>-32,17; 84,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,24; 22,92</t>
+          <t>-59,07; 27,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-76,56; 1,53</t>
+          <t>-72,88; -3,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 63,94</t>
+          <t>-3,13; 68,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,77; 18,95</t>
+          <t>-36,87; 16,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-62,95; -6,47</t>
+          <t>-55,14; 2,63</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,98</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>1,97</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>0,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 4,48</t>
+          <t>-1,91; 4,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 1,06</t>
+          <t>-4,64; 1,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 2,91</t>
+          <t>-3,78; 2,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,22</t>
+          <t>-0,73; 3,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,21</t>
+          <t>-1,27; 2,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 4,6</t>
+          <t>-0,09; 3,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,29</t>
+          <t>-0,77; 2,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,25</t>
+          <t>-2,04; 1,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,93</t>
+          <t>-1,12; 2,31</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-3,98%</t>
+          <t>-13,58%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 76,73</t>
+          <t>-22,75; 73,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,35; 19,61</t>
+          <t>-52,94; 26,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,78; 52,76</t>
+          <t>-44,37; 40,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,96; 152,19</t>
+          <t>-22,55; 164,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,52; 160,13</t>
+          <t>-33,94; 152,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,97; 208,27</t>
+          <t>-6,38; 187,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 82,17</t>
+          <t>-13,2; 67,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,77; 30,97</t>
+          <t>-37,16; 26,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 70,99</t>
+          <t>-19,62; 58,74</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,21</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,89</t>
+          <t>0,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 1,22</t>
+          <t>-5,23; 1,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,49; -0,38</t>
+          <t>-6,66; -0,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 1,66</t>
+          <t>-3,29; 3,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,79</t>
+          <t>-0,9; 4,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 2,43</t>
+          <t>-2,5; 2,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,2</t>
+          <t>-1,66; 2,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 2,12</t>
+          <t>-2,15; 1,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 0,04</t>
+          <t>-3,56; 0,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 1,09</t>
+          <t>-1,58; 2,18</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-27,94%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-15,16%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-51,58; 21,64</t>
+          <t>-52,57; 17,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-66,38; -5,5</t>
+          <t>-66,32; -7,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,71; 26,13</t>
+          <t>-34,13; 51,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 176,04</t>
+          <t>-18,35; 175,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,05; 99,28</t>
+          <t>-48,47; 97,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-38,49; 85,43</t>
+          <t>-30,57; 92,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,47; 42,92</t>
+          <t>-31,49; 38,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-52,79; 1,76</t>
+          <t>-51,42; 4,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,44; 21,56</t>
+          <t>-23,31; 44,89</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>1,88</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>1,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 0,63</t>
+          <t>-4,5; 0,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,62</t>
+          <t>-4,59; 0,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 3,06</t>
+          <t>-2,77; 3,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 8,31</t>
+          <t>1,67; 8,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 4,69</t>
+          <t>-1,35; 4,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,47</t>
+          <t>-0,89; 4,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,76</t>
+          <t>-0,56; 3,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,92</t>
+          <t>-2,14; 1,96</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,06</t>
+          <t>-0,72; 2,96</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-72,96; 20,89</t>
+          <t>-73,45; 20,86</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-69,24; 25,38</t>
+          <t>-73,69; 23,28</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,26; 94,46</t>
+          <t>-40,97; 96,42</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,86; 265,72</t>
+          <t>20,88; 270,55</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,59; 153,02</t>
+          <t>-24,96; 157,28</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 146,93</t>
+          <t>-14,25; 158,98</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 101,13</t>
+          <t>-9,4; 109,56</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-37,49; 52,62</t>
+          <t>-37,34; 56,55</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 86,77</t>
+          <t>-13,34; 80,78</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-2,06</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>0,69</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 5,51</t>
+          <t>-1,15; 5,61</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 2,31</t>
+          <t>-3,27; 2,38</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,29</t>
+          <t>-1,9; 3,28</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 3,4</t>
+          <t>-4,03; 3,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 4,04</t>
+          <t>-3,64; 4,58</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 1,91</t>
+          <t>-2,76; 3,66</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,46</t>
+          <t>-2,06; 3,23</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,64</t>
+          <t>-2,48; 2,54</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 1,5</t>
+          <t>-1,56; 2,73</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-27,57%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-12,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 221,94</t>
+          <t>-32,01; 249,46</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-68,4; 93,99</t>
+          <t>-63,74; 116,35</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-43,21; 152,24</t>
+          <t>-37,8; 157,76</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-41,1; 62,45</t>
+          <t>-42,67; 64,38</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 71,98</t>
+          <t>-40,25; 80,9</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-73,71; 29,11</t>
+          <t>-28,37; 70,03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 80,18</t>
+          <t>-29,1; 77,24</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-36,57; 58,69</t>
+          <t>-37,17; 56,15</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-58,64; 32,27</t>
+          <t>-22,3; 62,39</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>3,22</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>1,96</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,49</t>
+          <t>2,38</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,18; 8,96</t>
+          <t>-0,15; 8,85</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 5,35</t>
+          <t>-1,99; 5,53</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 6,6</t>
+          <t>-0,84; 6,72</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 8,74</t>
+          <t>-1,38; 8,65</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 4,84</t>
+          <t>-4,55; 4,98</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 6,1</t>
+          <t>-2,69; 5,76</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,21; 7,52</t>
+          <t>0,43; 7,64</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 4,09</t>
+          <t>-2,58; 4,22</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 5,18</t>
+          <t>-0,73; 5,25</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 390,13</t>
+          <t>-8,12; 329,71</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-35,19; 240,75</t>
+          <t>-35,37; 276,83</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 293,18</t>
+          <t>-15,08; 296,83</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 115,11</t>
+          <t>-11,53; 112,79</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-38,83; 62,53</t>
+          <t>-37,58; 65,58</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 86,23</t>
+          <t>-20,25; 78,81</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 117,88</t>
+          <t>4,43; 131,03</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-29,87; 68,95</t>
+          <t>-26,12; 67,07</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 82,11</t>
+          <t>-7,35; 89,63</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-1,64</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>-0,05</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,22</t>
+          <t>-0,29; 2,41</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,71; -0,29</t>
+          <t>-2,8; -0,31</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,3; -0,26</t>
+          <t>-2,33; 0,28</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,18</t>
+          <t>0,87; 3,23</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,28</t>
+          <t>-0,88; 1,26</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,71</t>
+          <t>-0,07; 1,97</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,44</t>
+          <t>0,58; 2,46</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,19</t>
+          <t>-1,45; 0,27</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,45</t>
+          <t>-0,74; 0,89</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-22,05%</t>
+          <t>-15,66%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-7,62%</t>
+          <t>-0,82%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 32,82</t>
+          <t>-3,56; 36,06</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-33,32; -3,96</t>
+          <t>-34,67; -4,88</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-41,11; -3,8</t>
+          <t>-29,32; 3,82</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15,42; 67,5</t>
+          <t>14,68; 68,54</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 27,4</t>
+          <t>-15,39; 27,67</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 36,65</t>
+          <t>-1,29; 42,93</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,39; 41,84</t>
+          <t>8,68; 41,73</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 3,2</t>
+          <t>-21,5; 4,44</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 7,37</t>
+          <t>-11,23; 14,87</t>
         </is>
       </c>
     </row>
